--- a/app-assets/templates/Mascara_Cadastros_Administrativo.xlsx
+++ b/app-assets/templates/Mascara_Cadastros_Administrativo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anderson.marley\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anderson.marley\Desktop\Mascaras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F840E87F-5901-4F23-903C-9DAEDCFA874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DF44E4-99A5-455F-BF0F-10AC46FCEEAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t>Razão Social</t>
   </si>
   <si>
-    <t>Objeto Do Contrato</t>
-  </si>
-  <si>
     <t>Cargo</t>
   </si>
   <si>
@@ -105,6 +102,9 @@
   </si>
   <si>
     <t>Tipo CT</t>
+  </si>
+  <si>
+    <t>Condição Fixa</t>
   </si>
 </sst>
 </file>
@@ -192,13 +192,13 @@
     <tableColumn id="2" xr3:uid="{90CF9C8F-9093-47CB-93BB-FE65C813BCB9}" name="Responsável"/>
     <tableColumn id="3" xr3:uid="{3AA7841C-5B90-4AAE-952F-5CFDE9799DCF}" name="Cartão CNPJ"/>
     <tableColumn id="4" xr3:uid="{0C62E6BD-84C3-4DC1-BFE1-6D80A04E97D3}" name="Razão Social"/>
-    <tableColumn id="5" xr3:uid="{76576920-7859-42B2-906C-3A8F24F42EB9}" name="Objeto Do Contrato"/>
     <tableColumn id="6" xr3:uid="{4DAE30C6-E952-4F23-B414-E51DC501CD17}" name="Cargo"/>
     <tableColumn id="7" xr3:uid="{690E1F3D-9A34-4A29-A405-825A921BE439}" name="CPF"/>
     <tableColumn id="8" xr3:uid="{AF2BDB8B-F4BE-4B69-A679-4F3FEB43ADB2}" name="E-mail"/>
     <tableColumn id="9" xr3:uid="{EAA50519-FE95-437C-804D-034039C19C0F}" name="Telefone"/>
     <tableColumn id="10" xr3:uid="{4EF7F99E-7BD1-4213-924E-2253695B8B1B}" name="Tipo CT"/>
     <tableColumn id="11" xr3:uid="{2AE57DB1-D2D4-40AF-8BBF-EC3C7C584855}" name="Tipo Contrato"/>
+    <tableColumn id="5" xr3:uid="{C30BC0E8-F8A4-4ACA-9E80-B725D8E334A6}" name="Condição Fixa"/>
     <tableColumn id="12" xr3:uid="{A159A206-7F2D-4020-B710-5E41DE97AEAC}" name="Hora"/>
     <tableColumn id="13" xr3:uid="{A348B190-AEDA-4EF6-8581-13D54F2FA82C}" name="A1 Equivalente"/>
     <tableColumn id="14" xr3:uid="{DB6BE516-1723-4D04-AEA5-A267D5B96ADE}" name="Documento"/>
@@ -580,9 +580,7 @@
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" customWidth="1"/>
-    <col min="6" max="20" width="18" customWidth="1"/>
+    <col min="4" max="20" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -602,10 +600,10 @@
         <v>23</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>25</v>
@@ -614,10 +612,10 @@
         <v>26</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>9</v>
